--- a/data/candidates_cleaned.xlsx
+++ b/data/candidates_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M304"/>
+  <dimension ref="A1:O302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,16 @@
           <t>reasoning</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>appearance_order</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>first_chapter_or_episode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +549,14 @@
           <t>Chitoge is the first girl introduced in the manga, holds a childhood promise, and is the canonical winner who marries Raku.</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -596,6 +614,14 @@
           <t>Introduced shortly after Chitoge, holds a childhood promise, but does not win.</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -653,6 +679,14 @@
           <t>Introduced as a hitman sent to kill Raku, later becomes a romantic interest.</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Chapter 14</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -699,7 +733,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -708,6 +742,14 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Introduced later in the series, holds a childhood promise, does not win.</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Chapter 33</t>
         </is>
       </c>
     </row>
@@ -751,12 +793,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -767,6 +809,14 @@
           <t>Automatically recovered missing major candidate: Yui Kanakura.</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Chapter 118</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -824,6 +874,14 @@
           <t>Eldest sister, introduced alongside the others, but often listed first in the quintuplet order.</t>
         </is>
       </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -881,6 +939,14 @@
           <t>Second sister, aggressive romantic interest.</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -938,6 +1004,14 @@
           <t>Third sister, shy and reserved.</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -984,7 +1058,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -993,6 +1067,14 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>Confirmed as the girl from the childhood promise and the canonical winner.</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -1052,6 +1134,14 @@
           <t>Fifth sister, but the first to interact with the protagonist in the opening chapter.</t>
         </is>
       </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1109,6 +1199,14 @@
           <t>Eriri is the first major heroine introduced as a romantic interest and childhood friend.</t>
         </is>
       </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1166,6 +1264,14 @@
           <t>Utaha is introduced as the second major romantic interest.</t>
         </is>
       </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1223,6 +1329,14 @@
           <t>Megumi is the titular heroine and the canonical winner of the series.</t>
         </is>
       </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1264,12 +1378,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1280,6 +1394,14 @@
           <t>Automatically recovered missing major candidate: Michiru Hyodo.</t>
         </is>
       </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1321,12 +1443,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1337,6 +1459,14 @@
           <t>Automatically recovered missing major candidate: Izumi Hashima.</t>
         </is>
       </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Episode 7</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1394,6 +1524,14 @@
           <t>First major conquest in the series.</t>
         </is>
       </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1451,6 +1589,14 @@
           <t>Second major conquest.</t>
         </is>
       </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Chapter 11</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1508,6 +1654,14 @@
           <t>Third major conquest.</t>
         </is>
       </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Chapter 23</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1565,6 +1719,14 @@
           <t>Fourth major conquest.</t>
         </is>
       </c>
+      <c r="N20" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Chapter 65</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1622,6 +1784,14 @@
           <t>Childhood friend and goddess host.</t>
         </is>
       </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Chapter 40</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1663,7 +1833,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1677,6 +1847,14 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>Sixth major conquest.</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Chapter 53</t>
         </is>
       </c>
     </row>
@@ -1736,6 +1914,14 @@
           <t>Seventh major conquest.</t>
         </is>
       </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Chapter 5</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1793,6 +1979,14 @@
           <t>Eighth major conquest.</t>
         </is>
       </c>
+      <c r="N24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Chapter 33</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1834,12 +2028,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1850,6 +2044,14 @@
           <t>Automatically recovered missing major candidate: Kanon Hinoki.</t>
         </is>
       </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1891,12 +2093,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -1907,6 +2109,14 @@
           <t>Automatically recovered missing major candidate: Chihiro Kosaka.</t>
         </is>
       </c>
+      <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Chapter 41</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1964,6 +2174,14 @@
           <t>Naru is the primary heroine, the first girl introduced, and the canonical winner who marries Keitaro.</t>
         </is>
       </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2021,6 +2239,14 @@
           <t>Introduced early as a tenant, but remains a supporting character.</t>
         </is>
       </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2078,6 +2304,14 @@
           <t>Introduced later as a rival for the childhood promise, but does not win.</t>
         </is>
       </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Chapter 13</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2135,6 +2369,14 @@
           <t>Introduced as a tenant and rival, does not win.</t>
         </is>
       </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2192,6 +2434,14 @@
           <t>Introduced as a tenant, does not win.</t>
         </is>
       </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2233,7 +2483,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2249,6 +2499,14 @@
           <t>Introduced as a tenant and childhood friend, does not win.</t>
         </is>
       </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2306,6 +2564,14 @@
           <t>Introduced late as a stepsister, does not win.</t>
         </is>
       </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Chapter 80</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2363,6 +2629,14 @@
           <t>The first girl introduced as a romantic interest and the canonical winner of the manga.</t>
         </is>
       </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2420,6 +2694,14 @@
           <t>A major romantic interest and primary contender throughout the series.</t>
         </is>
       </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2477,6 +2759,14 @@
           <t>Introduced as a major romantic rival to Aya and Tsukasa.</t>
         </is>
       </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2534,6 +2824,14 @@
           <t>Introduced later in the series as a romantic interest.</t>
         </is>
       </c>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Chapter 34</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2575,7 +2873,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2591,6 +2889,14 @@
           <t>The childhood friend character introduced late in the series.</t>
         </is>
       </c>
+      <c r="N38" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Chapter 59</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2648,6 +2954,14 @@
           <t>The primary heroine and the first girl introduced to the protagonist.</t>
         </is>
       </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2705,6 +3019,14 @@
           <t>Introduced shortly after Moka as a romantic rival.</t>
         </is>
       </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2762,6 +3084,14 @@
           <t>Introduced as a romantic interest following Kurumu.</t>
         </is>
       </c>
+      <c r="N41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2819,6 +3149,14 @@
           <t>Introduced as a romantic interest following Yukari.</t>
         </is>
       </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Chapter 14</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2860,7 +3198,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2874,6 +3212,14 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>Introduced as a romantic interest following Mizore.</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Chapter 17</t>
         </is>
       </c>
     </row>
@@ -2933,6 +3279,14 @@
           <t>Introduced as a romantic interest following Ruby.</t>
         </is>
       </c>
+      <c r="N44" t="n">
+        <v>6</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Chapter 27 (Rosario + Vampire Season II, Chapter 1)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2990,6 +3344,14 @@
           <t>Yukino is the primary heroine and the canonical winner of the series.</t>
         </is>
       </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3047,6 +3409,14 @@
           <t>Yui is a major romantic interest introduced shortly after Yukino.</t>
         </is>
       </c>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3088,7 +3458,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3102,6 +3472,14 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>Iroha is introduced later in the series as a romantic interest.</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Volume 7, Chapter 1</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3523,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -3161,6 +3539,14 @@
           <t>Automatically recovered missing major candidate: Shizuka Hiratsuka.</t>
         </is>
       </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3202,12 +3588,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -3218,6 +3604,14 @@
           <t>Automatically recovered missing major candidate: Saki Kawasaki.</t>
         </is>
       </c>
+      <c r="N49" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Volume 3, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3275,6 +3669,14 @@
           <t>Taiga is the primary heroine, the first to be introduced as a romantic interest, and the canonical winner who marries the protagonist.</t>
         </is>
       </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3332,6 +3734,14 @@
           <t>Minori is a major romantic interest introduced shortly after the initial plot setup.</t>
         </is>
       </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3389,6 +3799,14 @@
           <t>Ami is introduced as a romantic interest after the initial arc involving Taiga and Minori.</t>
         </is>
       </c>
+      <c r="N52" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3430,12 +3848,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -3446,6 +3864,14 @@
           <t>Automatically recovered missing major candidate: Yasuko Takasu.</t>
         </is>
       </c>
+      <c r="N53" t="n">
+        <v>99</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3487,12 +3913,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -3503,6 +3929,14 @@
           <t>Automatically recovered missing major candidate: Inko.</t>
         </is>
       </c>
+      <c r="N54" t="n">
+        <v>99</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3544,7 +3978,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3558,6 +3992,14 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>Koko Kaga is the primary heroine and the canonical winner who marries the protagonist, Banri Tada.</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
         </is>
       </c>
     </row>
@@ -3617,6 +4059,14 @@
           <t>Nana Hayashida (Linda) is the protagonist's childhood friend and a significant romantic interest, but she does not win.</t>
         </is>
       </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3674,6 +4124,14 @@
           <t>Setsuna is the first heroine introduced in the opening sequence of the visual novel and is considered the primary heroine of the Introductory Chapter.</t>
         </is>
       </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Introductory Chapter</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3731,6 +4189,14 @@
           <t>Kazusa is the second heroine introduced and shares a deep, complex history with the protagonist.</t>
         </is>
       </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Introductory Chapter</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3788,6 +4254,14 @@
           <t>Introduced in the Coda/Closing Chapter as a heroine route.</t>
         </is>
       </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Introductory Chapter</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3845,6 +4319,14 @@
           <t>Introduced in the Closing Chapter as a heroine route.</t>
         </is>
       </c>
+      <c r="N60" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Closing Chapter</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3886,7 +4368,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3902,6 +4384,14 @@
           <t>Introduced in the Closing Chapter as a heroine route.</t>
         </is>
       </c>
+      <c r="N61" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Closing Chapter</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3959,6 +4449,14 @@
           <t>Introduced in the Closing Chapter as a heroine route.</t>
         </is>
       </c>
+      <c r="N62" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Closing Chapter</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4016,6 +4514,14 @@
           <t>Yuzuki is the primary heroine, the first to move in with the protagonist, and the canonical winner who marries Haruto.</t>
         </is>
       </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4073,6 +4579,14 @@
           <t>Introduced as a romantic interest during the high school arc, but does not win.</t>
         </is>
       </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4130,6 +4644,14 @@
           <t>Introduced as a romantic interest during the college arc, but does not win.</t>
         </is>
       </c>
+      <c r="N65" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Chapter 75</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4171,12 +4693,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -4187,6 +4709,14 @@
           <t>Automatically recovered missing major candidate: Rin Eba.</t>
         </is>
       </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4228,12 +4758,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -4244,6 +4774,14 @@
           <t>Automatically recovered missing major candidate: Akari Kaga.</t>
         </is>
       </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4301,6 +4839,14 @@
           <t>She is the titular character and the primary romantic interest who eventually marries the protagonist.</t>
         </is>
       </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4358,6 +4904,14 @@
           <t>She is a significant romantic rival introduced after Suzuka.</t>
         </is>
       </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4399,12 +4953,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -4415,6 +4969,14 @@
           <t>Automatically recovered missing major candidate: Megumi Matsumoto.</t>
         </is>
       </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4472,6 +5034,14 @@
           <t>Hina is the first romantic interest introduced and is the canonical winner at the end of the manga.</t>
         </is>
       </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4529,6 +5099,14 @@
           <t>Rui is introduced shortly after Hina and serves as a primary romantic interest throughout the series but does not win.</t>
         </is>
       </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4586,6 +5164,14 @@
           <t>Introduced as a romantic interest following the main sisters.</t>
         </is>
       </c>
+      <c r="N73" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Chapter 20</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4643,6 +5229,14 @@
           <t>Introduced as a romantic interest during the college arc.</t>
         </is>
       </c>
+      <c r="N74" t="n">
+        <v>3</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Chapter 50</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4700,6 +5294,14 @@
           <t>Introduced first as the girl living in the protagonist's house; she is the primary focus of the early narrative.</t>
         </is>
       </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4757,6 +5359,14 @@
           <t>The central heroine of the anime original series, she is the one the protagonist ultimately chooses.</t>
         </is>
       </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4814,6 +5424,14 @@
           <t>Introduced as a childhood friend working at the family shop, she serves as a significant romantic obstacle.</t>
         </is>
       </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4871,6 +5489,14 @@
           <t>Madoka is the primary romantic interest and the first girl introduced in the manga. She is the canonical winner of the series.</t>
         </is>
       </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4928,6 +5554,14 @@
           <t>Hikaru is introduced shortly after Madoka as a romantic interest for Kyosuke, but she does not win the series.</t>
         </is>
       </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4985,6 +5619,14 @@
           <t>Juliet is the titular heroine and the primary romantic interest introduced in the first chapter. She marries the protagonist at the end of the manga.</t>
         </is>
       </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5042,6 +5684,14 @@
           <t>Hasuki is the protagonist's childhood friend who is introduced shortly after the start of the series as a romantic rival.</t>
         </is>
       </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5083,12 +5733,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -5099,6 +5749,14 @@
           <t>Automatically recovered missing major candidate: Chartreux Westia.</t>
         </is>
       </c>
+      <c r="N82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5140,12 +5798,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -5156,6 +5814,14 @@
           <t>Automatically recovered missing major candidate: Kochou Wang.</t>
         </is>
       </c>
+      <c r="N83" t="n">
+        <v>3</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5197,12 +5863,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -5213,6 +5879,14 @@
           <t>Automatically recovered missing major candidate: Teria Wang.</t>
         </is>
       </c>
+      <c r="N84" t="n">
+        <v>3</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5270,6 +5944,14 @@
           <t>Aki is the primary target of the protagonist's revenge and the eventual winner of the series.</t>
         </is>
       </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5327,6 +6009,14 @@
           <t>Yoshino is the maid and childhood friend who orchestrates the events, but does not win the protagonist.</t>
         </is>
       </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5384,6 +6074,14 @@
           <t>Neko is introduced later as a romantic rival who falls for the protagonist but is not the winner.</t>
         </is>
       </c>
+      <c r="N87" t="n">
+        <v>3</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Chapter 12</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5425,12 +6123,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -5441,6 +6139,14 @@
           <t>Automatically recovered missing major candidate: Tae Futaba.</t>
         </is>
       </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5482,12 +6188,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -5498,6 +6204,14 @@
           <t>Automatically recovered missing major candidate: Kojuurou Shuri.</t>
         </is>
       </c>
+      <c r="N89" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5555,6 +6269,14 @@
           <t>She is the primary heroine, the first witch introduced, and the canonical winner who marries Yamada.</t>
         </is>
       </c>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5612,6 +6334,14 @@
           <t>Introduced as a major rival/witch shortly after Shiraishi.</t>
         </is>
       </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5669,6 +6399,14 @@
           <t>Joins the club early on as a core member.</t>
         </is>
       </c>
+      <c r="N92" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5710,7 +6448,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5726,6 +6464,14 @@
           <t>Introduced during the witch hunt arc.</t>
         </is>
       </c>
+      <c r="N93" t="n">
+        <v>4</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Chapter 25</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5783,6 +6529,14 @@
           <t>Introduced as a key figure in the witch mystery.</t>
         </is>
       </c>
+      <c r="N94" t="n">
+        <v>5</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Chapter 36</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5840,6 +6594,14 @@
           <t>Introduced as a witch with the power of precognition.</t>
         </is>
       </c>
+      <c r="N95" t="n">
+        <v>6</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Chapter 40</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5881,12 +6643,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -5897,6 +6659,14 @@
           <t>Automatically recovered missing major candidate: Meiko Otsuka.</t>
         </is>
       </c>
+      <c r="N96" t="n">
+        <v>7</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Chapter 56</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5938,12 +6708,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -5954,6 +6724,14 @@
           <t>Automatically recovered missing major candidate: Mikoto Asuka.</t>
         </is>
       </c>
+      <c r="N97" t="n">
+        <v>8</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Chapter 69</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6011,6 +6789,14 @@
           <t>Subaru is the primary romantic interest and the first girl introduced in the series. She is the canonical winner in the light novel series.</t>
         </is>
       </c>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6052,7 +6838,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6066,6 +6852,14 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>Kanade is a major heroine and the primary antagonist/schemer, introduced shortly after Subaru.</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -6125,6 +6919,14 @@
           <t>Introduced as a rival/heroine later in the series.</t>
         </is>
       </c>
+      <c r="N100" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6182,6 +6984,14 @@
           <t>Introduced as a heroine later in the series.</t>
         </is>
       </c>
+      <c r="N101" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6239,6 +7049,14 @@
           <t>Aoi is the primary heroine, the childhood promise partner, and the canonical winner.</t>
         </is>
       </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6296,6 +7114,14 @@
           <t>Introduced early as a neighbor and romantic interest.</t>
         </is>
       </c>
+      <c r="N103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6353,6 +7179,14 @@
           <t>Taeko's younger sister, introduced shortly after.</t>
         </is>
       </c>
+      <c r="N104" t="n">
+        <v>6</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Chapter 19</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6410,6 +7244,14 @@
           <t>Introduced as Aoi's attendant and rival.</t>
         </is>
       </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6467,6 +7309,14 @@
           <t>Introduced as a foreign exchange student and romantic rival.</t>
         </is>
       </c>
+      <c r="N106" t="n">
+        <v>3</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6524,6 +7374,14 @@
           <t>Introduced later in the series.</t>
         </is>
       </c>
+      <c r="N107" t="n">
+        <v>4</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6581,6 +7439,14 @@
           <t>Introduced as a maid/caretaker figure.</t>
         </is>
       </c>
+      <c r="N108" t="n">
+        <v>5</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Chapter 11</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6638,6 +7504,14 @@
           <t>Akane is the primary heroine, the first to be introduced as a romantic interest, and the canonical winner in the manga.</t>
         </is>
       </c>
+      <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6695,6 +7569,14 @@
           <t>Introduced as a childhood friend with a promise, does not win.</t>
         </is>
       </c>
+      <c r="N110" t="n">
+        <v>3</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Chapter 34</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6752,6 +7634,14 @@
           <t>Introduced as a romantic rival/pursuer, does not win.</t>
         </is>
       </c>
+      <c r="N111" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Chapter 18</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6793,12 +7683,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yandere</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -6809,6 +7699,14 @@
           <t>Automatically recovered missing major candidate: Kodachi Kuno.</t>
         </is>
       </c>
+      <c r="N112" t="n">
+        <v>4</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Chapter 44</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6866,6 +7764,14 @@
           <t>Nagi is the first major heroine introduced and the primary focus of the series, though the manga ends without a definitive romantic winner.</t>
         </is>
       </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6923,6 +7829,14 @@
           <t>Introduced shortly after Nagi as a primary household figure.</t>
         </is>
       </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6980,6 +7894,14 @@
           <t>One of the earliest classmates to develop a crush on Hayate.</t>
         </is>
       </c>
+      <c r="N115" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7037,6 +7959,14 @@
           <t>Becomes a major romantic interest after the student council arc.</t>
         </is>
       </c>
+      <c r="N116" t="n">
+        <v>3</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7094,6 +8024,14 @@
           <t>Introduced as a recurring character who develops feelings for Hayate.</t>
         </is>
       </c>
+      <c r="N117" t="n">
+        <v>4</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Chapter 13</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7151,6 +8089,14 @@
           <t>A recurring character in the school setting.</t>
         </is>
       </c>
+      <c r="N118" t="n">
+        <v>4</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Chapter 13</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7192,7 +8138,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7206,6 +8152,14 @@
       <c r="M119" t="inlineStr">
         <is>
           <t>The primary childhood connection character introduced later in the series.</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>5</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Chapter 193</t>
         </is>
       </c>
     </row>
@@ -7265,6 +8219,14 @@
           <t>Introduced in the later stages of the manga.</t>
         </is>
       </c>
+      <c r="N120" t="n">
+        <v>6</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Chapter 270</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7306,12 +8268,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -7322,6 +8284,14 @@
           <t>Automatically recovered missing major candidate: Sakuya Aizawa.</t>
         </is>
       </c>
+      <c r="N121" t="n">
+        <v>4</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Chapter 13</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7379,6 +8349,14 @@
           <t>Kaname is the primary heroine and the canonical romantic partner of Sousuke Sagara, culminating in their marriage in the light novel epilogue.</t>
         </is>
       </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7436,6 +8414,14 @@
           <t>Teletha is a major romantic interest who develops feelings for Sousuke but does not end up with him.</t>
         </is>
       </c>
+      <c r="N123" t="n">
+        <v>2</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Volume 2, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7493,6 +8479,14 @@
           <t>Midori is the titular character and the primary romantic interest who appears in the first chapter. She is the canonical winner as the story focuses on her relationship with Seiji.</t>
         </is>
       </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7550,6 +8544,14 @@
           <t>Introduced as a classmate and romantic rival/interest for Seiji, but does not win.</t>
         </is>
       </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7607,6 +8609,14 @@
           <t>Seiji's childhood friend who harbors feelings for him, but does not win.</t>
         </is>
       </c>
+      <c r="N126" t="n">
+        <v>2</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7648,12 +8658,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -7664,6 +8674,14 @@
           <t>Automatically recovered missing major candidate: Rina.</t>
         </is>
       </c>
+      <c r="N127" t="n">
+        <v>3</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Chapter 20</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7705,12 +8723,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -7721,6 +8739,14 @@
           <t>Automatically recovered missing major candidate: Lucy Winfield.</t>
         </is>
       </c>
+      <c r="N128" t="n">
+        <v>4</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Chapter 30</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7778,6 +8804,14 @@
           <t>Rea is the primary heroine and the focus of the romantic narrative throughout the manga.</t>
         </is>
       </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7835,6 +8869,14 @@
           <t>Ranko is the childhood friend who harbors feelings for the protagonist but does not win.</t>
         </is>
       </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7876,7 +8918,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7892,6 +8934,14 @@
           <t>A secondary character introduced later in the series with limited romantic impact.</t>
         </is>
       </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Chapter 20</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7933,12 +8983,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -7949,6 +8999,14 @@
           <t>Automatically recovered missing major candidate: Erica Blandelli.</t>
         </is>
       </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7990,12 +9048,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -8006,6 +9064,14 @@
           <t>Automatically recovered missing major candidate: Yuri Mariya.</t>
         </is>
       </c>
+      <c r="N133" t="n">
+        <v>2</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8047,12 +9113,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -8063,6 +9129,14 @@
           <t>Automatically recovered missing major candidate: Liliana Kranjcar.</t>
         </is>
       </c>
+      <c r="N134" t="n">
+        <v>3</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Volume 3, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8104,12 +9178,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -8120,6 +9194,14 @@
           <t>Automatically recovered missing major candidate: Ena Seishuuin.</t>
         </is>
       </c>
+      <c r="N135" t="n">
+        <v>4</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Volume 4, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8177,6 +9259,14 @@
           <t>She is the first spirit encountered and the primary heroine of the series.</t>
         </is>
       </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8234,6 +9324,14 @@
           <t>She is a classmate and childhood acquaintance of Shido.</t>
         </is>
       </c>
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8291,6 +9389,14 @@
           <t>She is Shido's adoptive sister and childhood friend.</t>
         </is>
       </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8348,6 +9454,14 @@
           <t>Introduced as a transfer student and major romantic interest.</t>
         </is>
       </c>
+      <c r="N139" t="n">
+        <v>3</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Volume 3, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8405,6 +9519,14 @@
           <t>Introduced as the second spirit.</t>
         </is>
       </c>
+      <c r="N140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Volume 2, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8462,6 +9584,14 @@
           <t>Introduced as an analyst for Ratatoskr.</t>
         </is>
       </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8503,12 +9633,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -8519,6 +9649,14 @@
           <t>Automatically recovered missing major candidate: Kaguya Yamai.</t>
         </is>
       </c>
+      <c r="N142" t="n">
+        <v>4</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Volume 4, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8560,12 +9698,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -8576,6 +9714,14 @@
           <t>Automatically recovered missing major candidate: Yuzuru Yamai.</t>
         </is>
       </c>
+      <c r="N143" t="n">
+        <v>4</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Volume 4, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8617,12 +9763,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -8633,6 +9779,14 @@
           <t>Automatically recovered missing major candidate: Miku Izayoi.</t>
         </is>
       </c>
+      <c r="N144" t="n">
+        <v>5</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Volume 6, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8674,12 +9828,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -8690,6 +9844,14 @@
           <t>Automatically recovered missing major candidate: Natsumi.</t>
         </is>
       </c>
+      <c r="N145" t="n">
+        <v>6</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Volume 8, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8731,12 +9893,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -8747,6 +9909,14 @@
           <t>Automatically recovered missing major candidate: Yukina Himeragi.</t>
         </is>
       </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8788,12 +9958,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -8804,6 +9974,14 @@
           <t>Automatically recovered missing major candidate: Asagi Aiba.</t>
         </is>
       </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8845,12 +10023,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -8861,6 +10039,14 @@
           <t>Automatically recovered missing major candidate: Sayaka Kirasaka.</t>
         </is>
       </c>
+      <c r="N148" t="n">
+        <v>2</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8918,6 +10104,14 @@
           <t>Claire is the first major heroine introduced and the primary romantic interest throughout the series.</t>
         </is>
       </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8959,7 +10153,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -8975,6 +10169,14 @@
           <t>Restia is the childhood friend and a central figure in the protagonist's past.</t>
         </is>
       </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9032,6 +10234,14 @@
           <t>Introduced early as a rival and romantic interest.</t>
         </is>
       </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9089,6 +10299,14 @@
           <t>Introduced as a member of the team and romantic interest.</t>
         </is>
       </c>
+      <c r="N152" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9146,6 +10364,14 @@
           <t>Introduced as a princess and romantic interest.</t>
         </is>
       </c>
+      <c r="N153" t="n">
+        <v>3</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9203,6 +10429,14 @@
           <t>A spirit partner who develops romantic feelings for the protagonist.</t>
         </is>
       </c>
+      <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Volume 2, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9260,6 +10494,14 @@
           <t>Himari is the titular character, the first to appear as a romantic interest, and marries the protagonist in the manga ending.</t>
         </is>
       </c>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9317,6 +10559,14 @@
           <t>Childhood friend and fiancee who appears early in the narrative.</t>
         </is>
       </c>
+      <c r="N156" t="n">
+        <v>2</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9374,6 +10624,14 @@
           <t>Introduced as an antagonist/rival before becoming a romantic interest.</t>
         </is>
       </c>
+      <c r="N157" t="n">
+        <v>3</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9431,6 +10689,14 @@
           <t>Introduced later in the manga series.</t>
         </is>
       </c>
+      <c r="N158" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9488,6 +10754,14 @@
           <t>Childhood friend who is a romantic interest but does not win.</t>
         </is>
       </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9529,12 +10803,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -9545,6 +10819,14 @@
           <t>Automatically recovered missing major candidate: Ageha.</t>
         </is>
       </c>
+      <c r="N160" t="n">
+        <v>5</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Chapter 15</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9602,6 +10884,14 @@
           <t>Emile is the first heroine introduced and shares a childhood promise with the protagonist, Hayato Kisaragi.</t>
         </is>
       </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9659,6 +10949,14 @@
           <t>Claire is introduced shortly after Emile as the student council president.</t>
         </is>
       </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9700,12 +10998,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -9716,6 +11014,14 @@
           <t>Automatically recovered missing major candidate: Sakura Kirishima.</t>
         </is>
       </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Episode 3</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9757,12 +11063,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -9773,6 +11079,14 @@
           <t>Automatically recovered missing major candidate: Karen Kisaragi.</t>
         </is>
       </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9814,12 +11128,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -9830,6 +11144,14 @@
           <t>Automatically recovered missing major candidate: Liddy Steinberg.</t>
         </is>
       </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9887,6 +11209,14 @@
           <t>Julie is the first heroine introduced and the primary partner of the protagonist, though the series remains an open harem.</t>
         </is>
       </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9944,6 +11274,14 @@
           <t>Introduced shortly after Julie as a major romantic interest.</t>
         </is>
       </c>
+      <c r="N167" t="n">
+        <v>2</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10001,6 +11339,14 @@
           <t>Introduced as a classmate and romantic interest.</t>
         </is>
       </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10042,7 +11388,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10056,6 +11402,14 @@
       <c r="M169" t="inlineStr">
         <is>
           <t>Introduced as a classmate and romantic interest.</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
         </is>
       </c>
     </row>
@@ -10099,12 +11453,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -10115,6 +11469,14 @@
           <t>Automatically recovered missing major candidate: Rito Tsukimi.</t>
         </is>
       </c>
+      <c r="N170" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10172,6 +11534,14 @@
           <t>The protagonist's childhood friend and the first heroine to be established as a romantic interest.</t>
         </is>
       </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10229,6 +11599,14 @@
           <t>Student council president and major heroine, introduced shortly after the protagonist joins the club.</t>
         </is>
       </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10286,6 +11664,14 @@
           <t>A member of the food research club, introduced early as a core heroine.</t>
         </is>
       </c>
+      <c r="N173" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10343,6 +11729,14 @@
           <t>Introduced as a mysterious student who joins the club later in the narrative.</t>
         </is>
       </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10400,6 +11794,14 @@
           <t>A senior member of the club, introduced as a key heroine.</t>
         </is>
       </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10441,12 +11843,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -10457,6 +11859,14 @@
           <t>Automatically recovered missing major candidate: Oba Michiru.</t>
         </is>
       </c>
+      <c r="N176" t="n">
+        <v>99</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10514,6 +11924,14 @@
           <t>Stella is the primary heroine and the protagonist's fiancee, established early in the light novel.</t>
         </is>
       </c>
+      <c r="N177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Chapter 1 / Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10555,12 +11973,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -10571,6 +11989,14 @@
           <t>Automatically recovered missing major candidate: Shizuku Kurogane.</t>
         </is>
       </c>
+      <c r="N178" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Chapter 2 / Episode 2</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10612,12 +12038,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -10628,6 +12054,14 @@
           <t>Automatically recovered missing major candidate: Ayase Ayatsuji.</t>
         </is>
       </c>
+      <c r="N179" t="n">
+        <v>3</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Chapter 3 / Episode 5</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10669,12 +12103,12 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -10685,6 +12119,14 @@
           <t>Automatically recovered missing major candidate: Nene Saikyo.</t>
         </is>
       </c>
+      <c r="N180" t="n">
+        <v>4</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Chapter 4 / Episode 7</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10742,6 +12184,14 @@
           <t>Shana is the primary heroine and the canonical romantic partner of Yuji Sakai in the light novel series.</t>
         </is>
       </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10799,6 +12249,14 @@
           <t>Kazumi is a major romantic rival introduced shortly after the start of the series, but she does not win.</t>
         </is>
       </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10856,6 +12314,14 @@
           <t>The primary protagonist and canonical wife of Saito Hiraga.</t>
         </is>
       </c>
+      <c r="N183" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10913,6 +12379,14 @@
           <t>Introduced shortly after Louise as a maid and romantic rival.</t>
         </is>
       </c>
+      <c r="N184" t="n">
+        <v>2</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10970,6 +12444,14 @@
           <t>The Queen of Tristain, introduced early as a romantic interest.</t>
         </is>
       </c>
+      <c r="N185" t="n">
+        <v>3</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Chapter 5</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11027,6 +12509,14 @@
           <t>Introduced later in the series as a romantic interest.</t>
         </is>
       </c>
+      <c r="N186" t="n">
+        <v>4</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Chapter 10</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11084,6 +12574,14 @@
           <t>Classmate introduced as a romantic rival.</t>
         </is>
       </c>
+      <c r="N187" t="n">
+        <v>2</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11125,12 +12623,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -11141,6 +12639,14 @@
           <t>Automatically recovered missing major candidate: Tabitha.</t>
         </is>
       </c>
+      <c r="N188" t="n">
+        <v>2</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11182,12 +12688,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L189" t="n">
@@ -11198,6 +12704,14 @@
           <t>Automatically recovered missing major candidate: Montmorency Margarita la Fère de Montmorency.</t>
         </is>
       </c>
+      <c r="N189" t="n">
+        <v>2</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11255,6 +12769,14 @@
           <t>Mai is the primary heroine and the canonical romantic partner of Sakuta Azusagawa throughout the series.</t>
         </is>
       </c>
+      <c r="N190" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11312,6 +12834,14 @@
           <t>Tomoe is a major heroine introduced in the second volume of the light novel series.</t>
         </is>
       </c>
+      <c r="N191" t="n">
+        <v>2</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11353,12 +12883,12 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L192" t="n">
@@ -11369,6 +12899,14 @@
           <t>Automatically recovered missing major candidate: Rio Futaba.</t>
         </is>
       </c>
+      <c r="N192" t="n">
+        <v>1</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11410,12 +12948,12 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L193" t="n">
@@ -11426,6 +12964,14 @@
           <t>Automatically recovered missing major candidate: Kaede Azusagawa.</t>
         </is>
       </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11467,12 +13013,12 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -11483,6 +13029,14 @@
           <t>Automatically recovered missing major candidate: Nodoka Toyohama.</t>
         </is>
       </c>
+      <c r="N194" t="n">
+        <v>3</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Episode 7</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11524,12 +13078,12 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L195" t="n">
@@ -11540,6 +13094,14 @@
           <t>Automatically recovered missing major candidate: Shoko Makinohara.</t>
         </is>
       </c>
+      <c r="N195" t="n">
+        <v>1</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11597,6 +13159,14 @@
           <t>Emilia is the primary heroine and the first major romantic interest introduced in the series. The story is ongoing and features a harem dynamic, so no winner is declared.</t>
         </is>
       </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11638,12 +13208,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L197" t="n">
@@ -11654,6 +13224,14 @@
           <t>Automatically recovered missing major candidate: Rem.</t>
         </is>
       </c>
+      <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11695,12 +13273,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="L198" t="n">
@@ -11711,6 +13289,14 @@
           <t>Automatically recovered missing major candidate: Ram.</t>
         </is>
       </c>
+      <c r="N198" t="n">
+        <v>2</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11768,6 +13354,14 @@
           <t>She is the primary romantic interest and canonical partner of the protagonist, Koyomi Araragi, throughout the series.</t>
         </is>
       </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 1: Hitagi Crab</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11825,6 +13419,14 @@
           <t>Introduced early as a close friend and love interest, but does not end up with the protagonist.</t>
         </is>
       </c>
+      <c r="N200" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 1: Hitagi Crab</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11882,6 +13484,14 @@
           <t>A major character who develops feelings for the protagonist but remains a friend.</t>
         </is>
       </c>
+      <c r="N201" t="n">
+        <v>3</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 3: Suruga Monkey</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11939,6 +13549,14 @@
           <t>A major character with a crush on the protagonist, but never enters a romantic relationship with him.</t>
         </is>
       </c>
+      <c r="N202" t="n">
+        <v>4</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 4: Nadeko Snake</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11980,12 +13598,12 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L203" t="n">
@@ -11996,6 +13614,14 @@
           <t>Automatically recovered missing major candidate: Shinobu Oshino.</t>
         </is>
       </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 1: Hitagi Crab</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12037,12 +13663,12 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L204" t="n">
@@ -12053,6 +13679,14 @@
           <t>Automatically recovered missing major candidate: Mayoi Hachikuji.</t>
         </is>
       </c>
+      <c r="N204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 2: Mayoi Snail</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12094,12 +13728,12 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L205" t="n">
@@ -12110,6 +13744,14 @@
           <t>Automatically recovered missing major candidate: Karen Araragi.</t>
         </is>
       </c>
+      <c r="N205" t="n">
+        <v>1</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 1: Hitagi Crab</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12151,12 +13793,12 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L206" t="n">
@@ -12167,6 +13809,14 @@
           <t>Automatically recovered missing major candidate: Tsukihi Araragi.</t>
         </is>
       </c>
+      <c r="N206" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Bakemonogatari, Chapter 1: Hitagi Crab</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12208,12 +13858,12 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L207" t="n">
@@ -12224,6 +13874,14 @@
           <t>Automatically recovered missing major candidate: Sodachi Oikura.</t>
         </is>
       </c>
+      <c r="N207" t="n">
+        <v>5</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Owarimonogatari, Chapter 1: Sodachi Riddle</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12281,6 +13939,14 @@
           <t>The primary heroine and childhood friend of the protagonist, introduced first.</t>
         </is>
       </c>
+      <c r="N208" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12338,6 +14004,14 @@
           <t>Introduced shortly after Yozora as a major romantic interest in the Neighbors Club.</t>
         </is>
       </c>
+      <c r="N209" t="n">
+        <v>1</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12379,7 +14053,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12395,6 +14069,14 @@
           <t>Joins the club later as a romantic interest.</t>
         </is>
       </c>
+      <c r="N210" t="n">
+        <v>3</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Volume 2, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12452,6 +14134,14 @@
           <t>Joins the club later as a romantic interest.</t>
         </is>
       </c>
+      <c r="N211" t="n">
+        <v>2</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 2</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12493,12 +14183,12 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L212" t="n">
@@ -12509,6 +14199,14 @@
           <t>Automatically recovered missing major candidate: Kobato Hasegawa.</t>
         </is>
       </c>
+      <c r="N212" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12550,12 +14248,12 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="L213" t="n">
@@ -12566,6 +14264,14 @@
           <t>Automatically recovered missing major candidate: Maria Takayama.</t>
         </is>
       </c>
+      <c r="N213" t="n">
+        <v>1</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12623,6 +14329,14 @@
           <t>Masuzu is the first heroine introduced and initiates the fake relationship that drives the plot.</t>
         </is>
       </c>
+      <c r="N214" t="n">
+        <v>1</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12680,6 +14394,14 @@
           <t>Chiwa is the childhood friend who re-enters the protagonist's life as a romantic interest early in the series.</t>
         </is>
       </c>
+      <c r="N215" t="n">
+        <v>1</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12737,6 +14459,14 @@
           <t>Ai is introduced later as a transfer student with a childhood promise connection.</t>
         </is>
       </c>
+      <c r="N216" t="n">
+        <v>2</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12794,6 +14524,14 @@
           <t>Himeka is introduced as a romantic interest after the initial trio.</t>
         </is>
       </c>
+      <c r="N217" t="n">
+        <v>2</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12835,7 +14573,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -12851,6 +14589,14 @@
           <t>Lieselotte is a major heroine in the Trinity Seven series, introduced later in the story as a member of the Trinity Seven.</t>
         </is>
       </c>
+      <c r="N218" t="n">
+        <v>3</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Chapter 10: The Twin and the Demon Lord</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12892,12 +14638,12 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="L219" t="n">
@@ -12908,6 +14654,14 @@
           <t>Automatically recovered missing major candidate: Lilith Asami.</t>
         </is>
       </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Chapter 1: The Magus and the King</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12949,12 +14703,12 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L220" t="n">
@@ -12965,6 +14719,14 @@
           <t>Automatically recovered missing major candidate: Arata Kasuga.</t>
         </is>
       </c>
+      <c r="N220" t="n">
+        <v>99</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13006,12 +14768,12 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L221" t="n">
@@ -13022,6 +14784,14 @@
           <t>Automatically recovered missing major candidate: Arin Kannazuki.</t>
         </is>
       </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Chapter 1: The Magus and the King</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13063,12 +14833,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L222" t="n">
@@ -13079,6 +14849,14 @@
           <t>Automatically recovered missing major candidate: Levi Kazama.</t>
         </is>
       </c>
+      <c r="N222" t="n">
+        <v>1</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Chapter 1: The Magus and the King</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13120,12 +14898,12 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="L223" t="n">
@@ -13136,6 +14914,14 @@
           <t>Automatically recovered missing major candidate: Mira Yamana.</t>
         </is>
       </c>
+      <c r="N223" t="n">
+        <v>1</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Chapter 1: The Magus and the King</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13177,12 +14963,12 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L224" t="n">
@@ -13193,6 +14979,14 @@
           <t>Automatically recovered missing major candidate: Akio Fudo.</t>
         </is>
       </c>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Chapter 1: The Magus and the King</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13234,12 +15028,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="L225" t="n">
@@ -13250,6 +15044,14 @@
           <t>Automatically recovered missing major candidate: Yui Kurata.</t>
         </is>
       </c>
+      <c r="N225" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Chapter 2: The Grimoire and the Library</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13307,6 +15109,14 @@
           <t>Houki is the childhood friend and the first heroine introduced in the series.</t>
         </is>
       </c>
+      <c r="N226" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 1 / Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13364,6 +15174,14 @@
           <t>Introduced as the second childhood friend.</t>
         </is>
       </c>
+      <c r="N227" t="n">
+        <v>2</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 3 / Episode 2</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13421,6 +15239,14 @@
           <t>Introduced as the British representative.</t>
         </is>
       </c>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Volume 1, Chapter 2 / Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13478,6 +15304,14 @@
           <t>Introduced as the French representative.</t>
         </is>
       </c>
+      <c r="N229" t="n">
+        <v>3</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Volume 2, Chapter 1 / Episode 3</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13535,6 +15369,14 @@
           <t>Introduced as the German representative.</t>
         </is>
       </c>
+      <c r="N230" t="n">
+        <v>4</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Volume 2, Chapter 3 / Episode 5</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13576,12 +15418,12 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -13592,6 +15434,14 @@
           <t>Automatically recovered missing major candidate: Tatenashi Sarashiki.</t>
         </is>
       </c>
+      <c r="N231" t="n">
+        <v>5</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Volume 4, Chapter 1 / Episode 1 (Season 2)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13633,12 +15483,12 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -13649,6 +15499,14 @@
           <t>Automatically recovered missing major candidate: Kanzashi Sarashiki.</t>
         </is>
       </c>
+      <c r="N232" t="n">
+        <v>6</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Volume 6, Chapter 1 / Episode 5 (Season 2)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13706,6 +15564,14 @@
           <t>Erika is the first heroine introduced and is engaged to the protagonist due to the baby swap.</t>
         </is>
       </c>
+      <c r="N233" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13747,7 +15613,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -13763,6 +15629,14 @@
           <t>Introduced as the protagonist's academic rival and crush.</t>
         </is>
       </c>
+      <c r="N234" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13820,6 +15694,14 @@
           <t>Introduced as the protagonist's younger sister figure.</t>
         </is>
       </c>
+      <c r="N235" t="n">
+        <v>1</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13877,6 +15759,14 @@
           <t>Introduced later as a musician and romantic interest.</t>
         </is>
       </c>
+      <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Chapter 50</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13934,6 +15824,14 @@
           <t>Shiragiku is the first heroine introduced in the manga and has a confirmed childhood connection.</t>
         </is>
       </c>
+      <c r="N237" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13991,6 +15889,14 @@
           <t>Introduced as part of the main group at the cafe.</t>
         </is>
       </c>
+      <c r="N238" t="n">
+        <v>1</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14048,6 +15954,14 @@
           <t>Introduced as part of the main group at the cafe.</t>
         </is>
       </c>
+      <c r="N239" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14089,7 +16003,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -14103,6 +16017,14 @@
       <c r="M240" t="inlineStr">
         <is>
           <t>Introduced as part of the main group at the cafe.</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>1</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -14162,6 +16084,14 @@
           <t>Introduced as part of the main group at the cafe.</t>
         </is>
       </c>
+      <c r="N241" t="n">
+        <v>1</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14219,6 +16149,14 @@
           <t>Yuna is the eldest sister and the first of the three sisters to be introduced as a primary romantic interest in the manga.</t>
         </is>
       </c>
+      <c r="N242" t="n">
+        <v>1</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14276,6 +16214,14 @@
           <t>Asahi is the middle sister and is introduced as a romantic interest shortly after Yuna.</t>
         </is>
       </c>
+      <c r="N243" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14333,6 +16279,14 @@
           <t>Yae is the youngest sister and is introduced as a romantic interest after Yuna and Asahi.</t>
         </is>
       </c>
+      <c r="N244" t="n">
+        <v>1</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14390,6 +16344,14 @@
           <t>Tsukasa is the primary heroine and the canonical winner who marries the protagonist.</t>
         </is>
       </c>
+      <c r="N245" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14447,6 +16409,14 @@
           <t>Yuki is a significant romantic interest introduced later in the series.</t>
         </is>
       </c>
+      <c r="N246" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14488,12 +16458,12 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L247" t="n">
@@ -14504,6 +16474,14 @@
           <t>Automatically recovered missing major candidate: Sho Iketani.</t>
         </is>
       </c>
+      <c r="N247" t="n">
+        <v>99</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14545,12 +16523,12 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L248" t="n">
@@ -14561,6 +16539,14 @@
           <t>Automatically recovered missing major candidate: Misa Kawakami.</t>
         </is>
       </c>
+      <c r="N248" t="n">
+        <v>2</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Chapter 32</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14618,6 +16604,14 @@
           <t>Ritsu is the primary romantic interest and the first girl introduced in the series. The manga concludes with them officially becoming a couple.</t>
         </is>
       </c>
+      <c r="N249" t="n">
+        <v>1</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Chapter 1 / Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14659,12 +16653,12 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L250" t="n">
@@ -14675,6 +16669,14 @@
           <t>Automatically recovered missing major candidate: Sayaka Watanabe.</t>
         </is>
       </c>
+      <c r="N250" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Chapter 1 / Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14716,12 +16718,12 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="L251" t="n">
@@ -14732,6 +16734,14 @@
           <t>Automatically recovered missing major candidate: Mayumi Nishikino.</t>
         </is>
       </c>
+      <c r="N251" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Chapter 1 / Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14789,6 +16799,14 @@
           <t>Mashiro is the primary heroine and the eventual romantic partner of Sorata Kanda in the light novel series.</t>
         </is>
       </c>
+      <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14846,6 +16864,14 @@
           <t>Nanami is a major romantic interest who competes for Sorata's affection but does not win.</t>
         </is>
       </c>
+      <c r="N253" t="n">
+        <v>2</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Episode 2</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14887,12 +16913,12 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L254" t="n">
@@ -14903,6 +16929,14 @@
           <t>Automatically recovered missing major candidate: Misaki Kamiigusa.</t>
         </is>
       </c>
+      <c r="N254" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14944,12 +16978,12 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L255" t="n">
@@ -14960,6 +16994,14 @@
           <t>Automatically recovered missing major candidate: Rita Ainsworth.</t>
         </is>
       </c>
+      <c r="N255" t="n">
+        <v>3</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Episode 7</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15017,6 +17059,14 @@
           <t>Tsukiko is the primary heroine and the first to be introduced as a romantic interest. While the series ends with a strong focus on her, it remains an open-ended harem conclusion in the light novel.</t>
         </is>
       </c>
+      <c r="N256" t="n">
+        <v>1</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15074,6 +17124,14 @@
           <t>Introduced after Tsukiko as a major romantic interest. The series does not have a single canonical winner.</t>
         </is>
       </c>
+      <c r="N257" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15131,6 +17189,14 @@
           <t>Victorique is the primary protagonist and romantic partner of Kazuya Kujo, eventually marrying him. She is the first major heroine introduced.</t>
         </is>
       </c>
+      <c r="N258" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>The Black Reaper Sees the Golden Fairy</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15188,6 +17254,14 @@
           <t>Avril is a secondary character who develops a crush on Kazuya but is not the romantic winner.</t>
         </is>
       </c>
+      <c r="N259" t="n">
+        <v>2</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>The Golden Thread Tears the Short-Lived Moment</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15245,6 +17319,14 @@
           <t>He is Ririchiyo's devoted Secret Service agent and main love interest who eventually marries her.</t>
         </is>
       </c>
+      <c r="N260" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15302,6 +17384,14 @@
           <t>Nagisa is the primary heroine and the only one with a true route that leads to the After Story, resulting in marriage.</t>
         </is>
       </c>
+      <c r="N261" t="n">
+        <v>1</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15359,6 +17449,14 @@
           <t>Introduced as a transfer student and potential romantic interest.</t>
         </is>
       </c>
+      <c r="N262" t="n">
+        <v>2</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Episode 2</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15416,6 +17514,14 @@
           <t>Class representative introduced early in the school setting.</t>
         </is>
       </c>
+      <c r="N263" t="n">
+        <v>3</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Episode 3</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15473,6 +17579,14 @@
           <t>Introduced during the carving starfish arc.</t>
         </is>
       </c>
+      <c r="N264" t="n">
+        <v>4</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15530,6 +17644,14 @@
           <t>Revealed to be a childhood friend of Tomoya.</t>
         </is>
       </c>
+      <c r="N265" t="n">
+        <v>5</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Episode 5</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15587,6 +17709,14 @@
           <t>Twin sister of Kyou, introduced alongside her.</t>
         </is>
       </c>
+      <c r="N266" t="n">
+        <v>3</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Episode 3</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15628,12 +17758,12 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L267" t="n">
@@ -15644,6 +17774,14 @@
           <t>Automatically recovered missing major candidate: Yukine Miyazawa.</t>
         </is>
       </c>
+      <c r="N267" t="n">
+        <v>6</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Episode 7</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15701,6 +17839,14 @@
           <t>Ayu is the primary heroine and the first to be introduced in the narrative structure of the visual novel.</t>
         </is>
       </c>
+      <c r="N268" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15758,6 +17904,14 @@
           <t>The protagonist's cousin and childhood friend, introduced early in the story.</t>
         </is>
       </c>
+      <c r="N269" t="n">
+        <v>1</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15815,6 +17969,14 @@
           <t>Introduced as a major heroine in the school setting.</t>
         </is>
       </c>
+      <c r="N270" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Episode 2</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15872,6 +18034,14 @@
           <t>Introduced as a major heroine following the initial encounters.</t>
         </is>
       </c>
+      <c r="N271" t="n">
+        <v>3</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Episode 3</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15929,6 +18099,14 @@
           <t>Introduced as a major heroine later in the story.</t>
         </is>
       </c>
+      <c r="N272" t="n">
+        <v>4</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15986,6 +18164,14 @@
           <t>Misuzu is the primary heroine of the AIR visual novel and the first to be introduced in the Dream arc.</t>
         </is>
       </c>
+      <c r="N273" t="n">
+        <v>1</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16043,6 +18229,14 @@
           <t>Introduced as a major heroine in the Dream arc following Misuzu.</t>
         </is>
       </c>
+      <c r="N274" t="n">
+        <v>2</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Episode 2</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16100,6 +18294,14 @@
           <t>Introduced as a major heroine in the Dream arc.</t>
         </is>
       </c>
+      <c r="N275" t="n">
+        <v>3</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Episode 4</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16157,6 +18359,14 @@
           <t>Introduced as a major heroine in the Dream arc.</t>
         </is>
       </c>
+      <c r="N276" t="n">
+        <v>2</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Episode 2</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16214,6 +18424,14 @@
           <t>He is Hikari's lifelong rival and primary love interest who eventually proposes marriage to her.</t>
         </is>
       </c>
+      <c r="N277" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16255,7 +18473,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -16271,6 +18489,14 @@
           <t>Hikari's childhood friend who harbor romantic feelings for her but loses to Kei.</t>
         </is>
       </c>
+      <c r="N278" t="n">
+        <v>2</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Chapter 8</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16328,6 +18554,14 @@
           <t>He is the host club president and the main love interest of Haruhi Fujioka whom he eventually marries.</t>
         </is>
       </c>
+      <c r="N279" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16385,6 +18619,14 @@
           <t>One of the Hitachiin twins who develops strong romantic feelings for Haruhi but ultimately steps back.</t>
         </is>
       </c>
+      <c r="N280" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16426,7 +18668,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -16442,6 +18684,14 @@
           <t>Hikaru's twin who also has feelings for Haruhi but prioritizes his brother's and Tamaki's happiness.</t>
         </is>
       </c>
+      <c r="N281" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16499,6 +18749,14 @@
           <t>Haruhi's friend and co-manager of the club who shows subtle romantic interest.</t>
         </is>
       </c>
+      <c r="N282" t="n">
+        <v>1</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16556,6 +18814,14 @@
           <t>Cursed Cat of the Sohma family who develops a deep romantic bond with Tohru and eventually marries her.</t>
         </is>
       </c>
+      <c r="N283" t="n">
+        <v>1</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16613,6 +18879,14 @@
           <t>Cursed Rat who initially acts as Tohru's prince but later realizes his feelings for her are maternal.</t>
         </is>
       </c>
+      <c r="N284" t="n">
+        <v>1</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16670,6 +18944,14 @@
           <t>Sawako's classmate and main love interest who eventually marries her in the manga ending.</t>
         </is>
       </c>
+      <c r="N285" t="n">
+        <v>1</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16727,6 +19009,14 @@
           <t>Sawako's rival who actively pursues Kazehaya but is rejected.</t>
         </is>
       </c>
+      <c r="N286" t="n">
+        <v>2</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Chapter 11</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16784,6 +19074,14 @@
           <t>Sawako's classmate who briefly shows romantic interest but later supports her relationship with Kazehaya.</t>
         </is>
       </c>
+      <c r="N287" t="n">
+        <v>3</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Chapter 31</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16796,22 +19094,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Mimi Yoshioka</t>
+          <t>Atsushi Otani</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -16820,7 +19118,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Marriage</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -16830,15 +19128,23 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>A minor romantic interest/rival for the protagonist, not the main heroine.</t>
+          <t>Risa's main love interest who is short and acts tsundere, but eventually falls in love with and marries her in the manga ending.</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -16853,7 +19159,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Seishirou Kotobuki</t>
+          <t>Haruka Fukagawa</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -16868,11 +19174,11 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Childhood Friend</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -16882,20 +19188,28 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Dandere</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L289" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Omitted by Gemini during curation; backfilled with defaults.</t>
+          <t>Risa's childhood friend who returns and declares his obsessive love for her, but is rejected.</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>2</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Chapter 12</t>
         </is>
       </c>
     </row>
@@ -16925,7 +19239,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -16939,7 +19253,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Deredere</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -16948,11 +19262,19 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Omitted by Gemini during curation; backfilled with defaults.</t>
+          <t>Risa's younger classmate and co-worker who falls in love with her and tries to win her heart.</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>4</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Chapter 26</t>
         </is>
       </c>
     </row>
@@ -16982,7 +19304,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -16996,20 +19318,28 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Deredere</t>
+          <t>Onee-san</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Omitted by Gemini during curation; backfilled with defaults.</t>
+          <t>A handsome teacher who Risa and other girls have a major crush on, but acts as a mentor.</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>3</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Chapter 16</t>
         </is>
       </c>
     </row>
@@ -17020,11 +19350,11 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Haruka Fukagawa</t>
+          <t>Soichiro Arima</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -17033,40 +19363,48 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G292" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Childhood Friend</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Marriage</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Deredere</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L292" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Omitted by Gemini during curation; backfilled with defaults.</t>
+          <t>Yukino's rival and main love interest who she eventually marries during the main story.</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>1</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -17077,26 +19415,26 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Risa Koizumi</t>
+          <t>Tsubasa Shibahime</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -17110,20 +19448,28 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Automatically recovered missing major candidate: Risa Koizumi.</t>
+          <t>Soichiro's childhood acquaintance who has a crush on him but loses to Yukino.</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>2</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Chapter 6</t>
         </is>
       </c>
     </row>
@@ -17134,11 +19480,11 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Soichiro Arima</t>
+          <t>Takashi Kosuda</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -17167,12 +19513,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Kuudere</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L294" t="n">
@@ -17180,7 +19526,15 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Yukino's rival and main love interest who she eventually marries during the main story.</t>
+          <t>Yamada's main love interest who she eventually marries.</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>1</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -17191,11 +19545,11 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Tsubasa Shibahime</t>
+          <t>Mikoto Urabe</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -17204,13 +19558,13 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -17224,20 +19578,28 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Tsundere</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Blonde</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Soichiro's childhood acquaintance who has a crush on him but loses to Yukino.</t>
+          <t>Mikoto Urabe is the titular character and the sole primary romantic interest throughout the manga series. She is the first girl introduced and the canonical winner.</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>1</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -17248,16 +19610,16 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Takashi Kosuda</t>
+          <t>Non Katagiri</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -17281,7 +19643,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -17294,7 +19656,15 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Yamada's main love interest who she eventually marries.</t>
+          <t>Akkun's extremely sweet and devoted girlfriend whom he eventually proposes to.</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>1</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -17305,11 +19675,11 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Mikoto Urabe</t>
+          <t>Chiho Kagari</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -17318,13 +19688,13 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -17338,20 +19708,28 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Kuudere</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blonde</t>
         </is>
       </c>
       <c r="L297" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Mikoto Urabe is the titular character and the sole primary romantic interest throughout the manga series. She is the first girl introduced and the canonical winner.</t>
+          <t>Akkun's younger sister who acts tsundere towards Akkun and Non.</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>2</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Chapter 2</t>
         </is>
       </c>
     </row>
@@ -17362,16 +19740,16 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Non Katagiri</t>
+          <t>Livius I</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -17395,12 +19773,12 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Deredere</t>
+          <t>Kuudere</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L298" t="n">
@@ -17408,7 +19786,15 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Akkun's extremely sweet and devoted girlfriend whom he eventually proposes to.</t>
+          <t>The Sun King who marries Nike Remercier.</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>1</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Chapter 1</t>
         </is>
       </c>
     </row>
@@ -17419,11 +19805,11 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Chiho Kagari</t>
+          <t>Aoi Oribe</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -17435,14 +19821,14 @@
         <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Childhood Friend</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -17452,20 +19838,28 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Tsundere</t>
+          <t>Genki</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Blonde</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="L299" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Akkun's younger sister who acts tsundere towards Akkun and Non.</t>
+          <t>She is the first heroine introduced and the protagonist's childhood friend.</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>1</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
         </is>
       </c>
     </row>
@@ -17476,45 +19870,45 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Livius I</t>
+          <t>Nanaka Yatsushiro</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E300" t="n">
         <v>1</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Childhood Promise</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Marriage</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Kuudere</t>
+          <t>Dandere</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="L300" t="n">
@@ -17522,7 +19916,15 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>The Sun King who marries Nike Remercier.</t>
+          <t>She is the primary romantic interest and the focus of the childhood promise plotline.</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
         </is>
       </c>
     </row>
@@ -17537,7 +19939,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Aoi Oribe</t>
+          <t>Shuri Wakatsuki</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -17549,10 +19951,10 @@
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -17566,12 +19968,12 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Genki</t>
+          <t>Tsundere</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="L301" t="n">
@@ -17579,7 +19981,15 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>She is the first heroine introduced and the protagonist's childhood friend.</t>
+          <t>Childhood friend introduced shortly after the main group is established.</t>
+        </is>
+      </c>
+      <c r="N301" t="n">
+        <v>1</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
         </is>
       </c>
     </row>
@@ -17594,7 +20004,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Nanaka Yatsushiro</t>
+          <t>Asami Hoshino</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -17603,17 +20013,17 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Childhood Promise</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -17623,134 +20033,28 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Dandere</t>
+          <t>Deredere</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="L302" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>She is the primary romantic interest and the focus of the childhood promise plotline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>C0302</t>
-        </is>
-      </c>
-      <c r="B303" t="n">
-        <v>70</v>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Shuri Wakatsuki</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E303" t="n">
-        <v>0</v>
-      </c>
-      <c r="F303" t="n">
-        <v>0</v>
-      </c>
-      <c r="G303" t="n">
-        <v>3</v>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>Childhood Friend</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>Tsundere</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="L303" t="n">
-        <v>1</v>
-      </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>Childhood friend introduced shortly after the main group is established.</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>C0303</t>
-        </is>
-      </c>
-      <c r="B304" t="n">
-        <v>70</v>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Asami Hoshino</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="E304" t="n">
-        <v>0</v>
-      </c>
-      <c r="F304" t="n">
-        <v>0</v>
-      </c>
-      <c r="G304" t="n">
-        <v>4</v>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>Deredere</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="L304" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
           <t>Introduced later in the series as a classmate.</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>1</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Episode 1</t>
         </is>
       </c>
     </row>
